--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/79.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/2_fold/79.xlsx
@@ -426,13 +426,13 @@
         <v>-3.16146295027201</v>
       </c>
       <c r="E2">
-        <v>-6.546232073565096</v>
+        <v>-12.3324154867237</v>
       </c>
       <c r="F2">
-        <v>-1.567608418877112</v>
+        <v>-2.327148430912812</v>
       </c>
       <c r="G2">
-        <v>-12.70777525637352</v>
+        <v>-13.88116396987102</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.943256603601692</v>
       </c>
       <c r="E3">
-        <v>-7.834682822866655</v>
+        <v>-13.34081519639207</v>
       </c>
       <c r="F3">
-        <v>-1.548406862480219</v>
+        <v>-2.363475654995181</v>
       </c>
       <c r="G3">
-        <v>-12.40147356333804</v>
+        <v>-13.264876823182</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.695472349222974</v>
       </c>
       <c r="E4">
-        <v>-8.870385743784448</v>
+        <v>-13.28977222920992</v>
       </c>
       <c r="F4">
-        <v>-1.944388846938258</v>
+        <v>-2.485651563234081</v>
       </c>
       <c r="G4">
-        <v>-11.7813133770481</v>
+        <v>-13.18419045622135</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.430916211208428</v>
       </c>
       <c r="E5">
-        <v>-7.485019808218015</v>
+        <v>-14.24180870798905</v>
       </c>
       <c r="F5">
-        <v>-0.9511274573048861</v>
+        <v>-2.175361701493442</v>
       </c>
       <c r="G5">
-        <v>-12.23695749292903</v>
+        <v>-12.73977515282679</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.140862626251463</v>
       </c>
       <c r="E6">
-        <v>-9.657855377028563</v>
+        <v>-14.63601491409647</v>
       </c>
       <c r="F6">
-        <v>-0.8565436388858357</v>
+        <v>-2.314686471705096</v>
       </c>
       <c r="G6">
-        <v>-11.21295558493503</v>
+        <v>-12.75686378154792</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.819822253388949</v>
       </c>
       <c r="E7">
-        <v>-10.50850366094597</v>
+        <v>-15.13901864406911</v>
       </c>
       <c r="F7">
-        <v>-1.19897249912029</v>
+        <v>-2.569011003345198</v>
       </c>
       <c r="G7">
-        <v>-10.40350597281102</v>
+        <v>-12.07848921236534</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.455006596300208</v>
       </c>
       <c r="E8">
-        <v>-10.913649425683</v>
+        <v>-16.20875297858255</v>
       </c>
       <c r="F8">
-        <v>-1.201252994580197</v>
+        <v>-2.217765828842749</v>
       </c>
       <c r="G8">
-        <v>-10.22267013796297</v>
+        <v>-11.88164559705688</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.041440677316047</v>
       </c>
       <c r="E9">
-        <v>-11.29942876601234</v>
+        <v>-16.47229084998822</v>
       </c>
       <c r="F9">
-        <v>-1.131902903985225</v>
+        <v>-1.955638076268276</v>
       </c>
       <c r="G9">
-        <v>-10.263466938316</v>
+        <v>-10.9220925300391</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.5765010550585966</v>
       </c>
       <c r="E10">
-        <v>-12.91627808797942</v>
+        <v>-16.4715017398365</v>
       </c>
       <c r="F10">
-        <v>-1.24348730661193</v>
+        <v>-1.994896892589153</v>
       </c>
       <c r="G10">
-        <v>-9.005392197144259</v>
+        <v>-10.30224041161092</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.07410502712115165</v>
       </c>
       <c r="E11">
-        <v>-12.72216945029091</v>
+        <v>-17.29746333563913</v>
       </c>
       <c r="F11">
-        <v>-1.121266666533279</v>
+        <v>-2.126255253488084</v>
       </c>
       <c r="G11">
-        <v>-8.845186466055184</v>
+        <v>-10.15742371451416</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.4367923763242521</v>
       </c>
       <c r="E12">
-        <v>-13.60628431106378</v>
+        <v>-18.27826080284268</v>
       </c>
       <c r="F12">
-        <v>-0.5165501788156123</v>
+        <v>-1.966715833545914</v>
       </c>
       <c r="G12">
-        <v>-7.904237564993679</v>
+        <v>-9.521555983391789</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.9209251813572398</v>
       </c>
       <c r="E13">
-        <v>-14.17405737164712</v>
+        <v>-18.90886364434803</v>
       </c>
       <c r="F13">
-        <v>-1.086809896046431</v>
+        <v>-1.886240768731344</v>
       </c>
       <c r="G13">
-        <v>-7.91004516633661</v>
+        <v>-9.456480563713699</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.337095575805418</v>
       </c>
       <c r="E14">
-        <v>-15.64754614510376</v>
+        <v>-19.19205035853146</v>
       </c>
       <c r="F14">
-        <v>-0.6894263139428551</v>
+        <v>-1.686087323397317</v>
       </c>
       <c r="G14">
-        <v>-6.792461118474155</v>
+        <v>-8.794557601572018</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.654076894362837</v>
       </c>
       <c r="E15">
-        <v>-14.81075297416598</v>
+        <v>-19.69584735186714</v>
       </c>
       <c r="F15">
-        <v>0.04935066914167559</v>
+        <v>-1.500869342335764</v>
       </c>
       <c r="G15">
-        <v>-7.277038811286102</v>
+        <v>-8.081699012457719</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.859086406804302</v>
       </c>
       <c r="E16">
-        <v>-16.63846914151726</v>
+        <v>-20.79127345163596</v>
       </c>
       <c r="F16">
-        <v>0.2045858920589002</v>
+        <v>-1.191087269813041</v>
       </c>
       <c r="G16">
-        <v>-5.779346015425098</v>
+        <v>-8.261318240326313</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.954948257321732</v>
       </c>
       <c r="E17">
-        <v>-17.75756023941496</v>
+        <v>-21.31016321492607</v>
       </c>
       <c r="F17">
-        <v>0.4410383969836023</v>
+        <v>-1.250930187726083</v>
       </c>
       <c r="G17">
-        <v>-6.739212371793808</v>
+        <v>-7.381896757043575</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>1.963034594500533</v>
       </c>
       <c r="E18">
-        <v>-17.09565049094306</v>
+        <v>-21.84280010770135</v>
       </c>
       <c r="F18">
-        <v>0.06737345872438444</v>
+        <v>-1.007927781747445</v>
       </c>
       <c r="G18">
-        <v>-5.99153428206783</v>
+        <v>-7.528181997972835</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>1.91509885194929</v>
       </c>
       <c r="E19">
-        <v>-18.7125953367706</v>
+        <v>-22.94532819883564</v>
       </c>
       <c r="F19">
-        <v>1.002968051611869</v>
+        <v>-0.467723718992401</v>
       </c>
       <c r="G19">
-        <v>-4.672523456767212</v>
+        <v>-7.508852045020232</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>1.843642503107987</v>
       </c>
       <c r="E20">
-        <v>-21.47635811930041</v>
+        <v>-23.64280189588204</v>
       </c>
       <c r="F20">
-        <v>1.196835845093454</v>
+        <v>-0.09807884773896922</v>
       </c>
       <c r="G20">
-        <v>-4.981458085722829</v>
+        <v>-7.977872310813733</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.78113158572488</v>
       </c>
       <c r="E21">
-        <v>-19.84002192979723</v>
+        <v>-24.52421301608246</v>
       </c>
       <c r="F21">
-        <v>1.035839326889759</v>
+        <v>-0.03414959342791737</v>
       </c>
       <c r="G21">
-        <v>-5.277947295212609</v>
+        <v>-6.829977518248453</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.751835719920277</v>
       </c>
       <c r="E22">
-        <v>-21.11146527872362</v>
+        <v>-24.53200028731651</v>
       </c>
       <c r="F22">
-        <v>1.302571973856394</v>
+        <v>0.1885636097539521</v>
       </c>
       <c r="G22">
-        <v>-4.486917791551195</v>
+        <v>-7.184174626180202</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.770545230757619</v>
       </c>
       <c r="E23">
-        <v>-20.65520594221193</v>
+        <v>-25.23135123588174</v>
       </c>
       <c r="F23">
-        <v>0.9177224189245777</v>
+        <v>0.188390480966767</v>
       </c>
       <c r="G23">
-        <v>-4.44750860194834</v>
+        <v>-6.733996104100765</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.849263996458273</v>
       </c>
       <c r="E24">
-        <v>-21.37263166646281</v>
+        <v>-25.07857535729792</v>
       </c>
       <c r="F24">
-        <v>1.512165494112725</v>
+        <v>0.2344692461148923</v>
       </c>
       <c r="G24">
-        <v>-4.497835925431231</v>
+        <v>-6.947124238796297</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.991554155763382</v>
       </c>
       <c r="E25">
-        <v>-21.62727751242203</v>
+        <v>-25.15285138863115</v>
       </c>
       <c r="F25">
-        <v>1.669121236125565</v>
+        <v>0.1219926917953726</v>
       </c>
       <c r="G25">
-        <v>-5.063404136948693</v>
+        <v>-7.555850669149454</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>2.195832795612593</v>
       </c>
       <c r="E26">
-        <v>-21.27948759608088</v>
+        <v>-25.1928385072666</v>
       </c>
       <c r="F26">
-        <v>1.489902291795086</v>
+        <v>0.5165556828924164</v>
       </c>
       <c r="G26">
-        <v>-4.521578036742815</v>
+        <v>-7.182767434845592</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.458810523650704</v>
       </c>
       <c r="E27">
-        <v>-21.27566248845072</v>
+        <v>-25.77812566000674</v>
       </c>
       <c r="F27">
-        <v>1.743889677902248</v>
+        <v>0.4999170952397855</v>
       </c>
       <c r="G27">
-        <v>-5.151005060958908</v>
+        <v>-7.516122968706482</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.771218946399209</v>
       </c>
       <c r="E28">
-        <v>-21.1573125785384</v>
+        <v>-25.51070038280103</v>
       </c>
       <c r="F28">
-        <v>1.590275569992302</v>
+        <v>0.4134421653267395</v>
       </c>
       <c r="G28">
-        <v>-4.521896547582931</v>
+        <v>-6.92956698142106</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>3.122617194894535</v>
       </c>
       <c r="E29">
-        <v>-20.31336757769927</v>
+        <v>-25.27962401111022</v>
       </c>
       <c r="F29">
-        <v>1.356545080353199</v>
+        <v>0.2788250070651946</v>
       </c>
       <c r="G29">
-        <v>-5.018494108492362</v>
+        <v>-7.53558084814405</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>3.500528743397309</v>
       </c>
       <c r="E30">
-        <v>-21.1271851835881</v>
+        <v>-25.1505671224025</v>
       </c>
       <c r="F30">
-        <v>1.702747982474808</v>
+        <v>0.3834635490194254</v>
       </c>
       <c r="G30">
-        <v>-5.176253571899565</v>
+        <v>-7.36465017827468</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>3.886570894735995</v>
       </c>
       <c r="E31">
-        <v>-21.06043892438678</v>
+        <v>-25.48300676968707</v>
       </c>
       <c r="F31">
-        <v>1.330980005568001</v>
+        <v>0.400202369127795</v>
       </c>
       <c r="G31">
-        <v>-4.21468762080204</v>
+        <v>-6.677990411132202</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>4.263531754608645</v>
       </c>
       <c r="E32">
-        <v>-21.57604765073027</v>
+        <v>-24.58205894341467</v>
       </c>
       <c r="F32">
-        <v>1.305626992837919</v>
+        <v>0.4734888616208701</v>
       </c>
       <c r="G32">
-        <v>-5.515804402675167</v>
+        <v>-7.257429508662249</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>4.611838851204235</v>
       </c>
       <c r="E33">
-        <v>-20.15375136006346</v>
+        <v>-24.34101071133295</v>
       </c>
       <c r="F33">
-        <v>1.360635558588223</v>
+        <v>0.4544761729918158</v>
       </c>
       <c r="G33">
-        <v>-5.143146719739657</v>
+        <v>-7.162977990844952</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>4.911634746668469</v>
       </c>
       <c r="E34">
-        <v>-19.1159469142153</v>
+        <v>-24.0085087658785</v>
       </c>
       <c r="F34">
-        <v>1.268590686258753</v>
+        <v>0.3388443672350328</v>
       </c>
       <c r="G34">
-        <v>-4.684522438907968</v>
+        <v>-6.959543550816224</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.155156503191401</v>
       </c>
       <c r="E35">
-        <v>-18.9009974620988</v>
+        <v>-23.19832521989889</v>
       </c>
       <c r="F35">
-        <v>1.971554861418053</v>
+        <v>0.4170836684294461</v>
       </c>
       <c r="G35">
-        <v>-4.661816793199056</v>
+        <v>-7.306991883979943</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.341267890142318</v>
       </c>
       <c r="E36">
-        <v>-19.01510279003714</v>
+        <v>-22.55104723492436</v>
       </c>
       <c r="F36">
-        <v>1.458308359052313</v>
+        <v>0.3535661127175856</v>
       </c>
       <c r="G36">
-        <v>-4.796562543035595</v>
+        <v>-7.335644805867412</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.474506747365574</v>
       </c>
       <c r="E37">
-        <v>-17.500347708857</v>
+        <v>-22.50465586442603</v>
       </c>
       <c r="F37">
-        <v>1.732908839610738</v>
+        <v>0.2718021082242604</v>
       </c>
       <c r="G37">
-        <v>-4.688587368236332</v>
+        <v>-7.204635031540756</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.562676341201575</v>
       </c>
       <c r="E38">
-        <v>-17.3313493868384</v>
+        <v>-22.21057112372625</v>
       </c>
       <c r="F38">
-        <v>1.317378212814033</v>
+        <v>0.3657729347652391</v>
       </c>
       <c r="G38">
-        <v>-5.489642131127622</v>
+        <v>-6.75173872434197</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.610839722694336</v>
       </c>
       <c r="E39">
-        <v>-15.8986326889576</v>
+        <v>-21.12259173186284</v>
       </c>
       <c r="F39">
-        <v>1.920338561637765</v>
+        <v>0.1970643160414806</v>
       </c>
       <c r="G39">
-        <v>-5.321807804343313</v>
+        <v>-7.075977538090694</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.622806604749655</v>
       </c>
       <c r="E40">
-        <v>-16.1359471840583</v>
+        <v>-20.45365890304065</v>
       </c>
       <c r="F40">
-        <v>1.533638433928094</v>
+        <v>0.3131069920300522</v>
       </c>
       <c r="G40">
-        <v>-5.436137531477345</v>
+        <v>-7.409983147354771</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.601748909745289</v>
       </c>
       <c r="E41">
-        <v>-14.84691498517127</v>
+        <v>-20.03778954666292</v>
       </c>
       <c r="F41">
-        <v>1.961707229733572</v>
+        <v>0.1314890957010662</v>
       </c>
       <c r="G41">
-        <v>-5.372229114631484</v>
+        <v>-7.430673298239345</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.551353626448218</v>
       </c>
       <c r="E42">
-        <v>-16.50265082477271</v>
+        <v>-19.05148907445396</v>
       </c>
       <c r="F42">
-        <v>1.592257024819798</v>
+        <v>0.3924587906464252</v>
       </c>
       <c r="G42">
-        <v>-5.21097386421678</v>
+        <v>-7.315978066862556</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.475480499244904</v>
       </c>
       <c r="E43">
-        <v>-15.00580023761391</v>
+        <v>-18.68376789696497</v>
       </c>
       <c r="F43">
-        <v>1.266262973856886</v>
+        <v>0.1827981726304675</v>
       </c>
       <c r="G43">
-        <v>-5.096876493351356</v>
+        <v>-7.612642196239941</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.377636332075846</v>
       </c>
       <c r="E44">
-        <v>-13.44224077015571</v>
+        <v>-18.54097633840604</v>
       </c>
       <c r="F44">
-        <v>1.196519408745585</v>
+        <v>0.117330640052417</v>
       </c>
       <c r="G44">
-        <v>-5.285928341427643</v>
+        <v>-7.572825730480872</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.258246052080303</v>
       </c>
       <c r="E45">
-        <v>-12.31711090299171</v>
+        <v>-18.06805431805914</v>
       </c>
       <c r="F45">
-        <v>1.601504918504652</v>
+        <v>0.4437107102250334</v>
       </c>
       <c r="G45">
-        <v>-5.718949050054284</v>
+        <v>-7.59690462784471</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.117058897164527</v>
       </c>
       <c r="E46">
-        <v>-12.18113061100549</v>
+        <v>-17.24980523568672</v>
       </c>
       <c r="F46">
-        <v>1.233852270854953</v>
+        <v>0.3401316501789832</v>
       </c>
       <c r="G46">
-        <v>-5.137914787579066</v>
+        <v>-7.750523450330407</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.955447296652927</v>
       </c>
       <c r="E47">
-        <v>-12.09818267442602</v>
+        <v>-16.52387788785391</v>
       </c>
       <c r="F47">
-        <v>1.008306051155509</v>
+        <v>0.06511532918435299</v>
       </c>
       <c r="G47">
-        <v>-5.733190661798806</v>
+        <v>-8.181637010033239</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.771357392617546</v>
       </c>
       <c r="E48">
-        <v>-12.18140887616426</v>
+        <v>-16.56136062006049</v>
       </c>
       <c r="F48">
-        <v>1.499743296540344</v>
+        <v>0.1680267251037468</v>
       </c>
       <c r="G48">
-        <v>-5.877846798103211</v>
+        <v>-8.847376880767127</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.562078804093635</v>
       </c>
       <c r="E49">
-        <v>-10.71731466672438</v>
+        <v>-15.60084743696739</v>
       </c>
       <c r="F49">
-        <v>1.461649993155206</v>
+        <v>0.2214116907445637</v>
       </c>
       <c r="G49">
-        <v>-6.348616262772759</v>
+        <v>-8.38077024834811</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.326878006651127</v>
       </c>
       <c r="E50">
-        <v>-10.00726504578639</v>
+        <v>-15.54661065027646</v>
       </c>
       <c r="F50">
-        <v>0.8603795138331848</v>
+        <v>0.203136249104001</v>
       </c>
       <c r="G50">
-        <v>-5.814079361465269</v>
+        <v>-8.335946374463285</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.061062530694365</v>
       </c>
       <c r="E51">
-        <v>-9.696754354296907</v>
+        <v>-14.92852558770415</v>
       </c>
       <c r="F51">
-        <v>1.02394728445517</v>
+        <v>-0.04071523346250625</v>
       </c>
       <c r="G51">
-        <v>-5.450653271403936</v>
+        <v>-8.756252756931204</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>3.763066440511851</v>
       </c>
       <c r="E52">
-        <v>-9.360589276453961</v>
+        <v>-14.06560456432187</v>
       </c>
       <c r="F52">
-        <v>0.6334085022009258</v>
+        <v>0.2660987986559858</v>
       </c>
       <c r="G52">
-        <v>-6.188841304541217</v>
+        <v>-8.036407815291085</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>3.433023180414477</v>
       </c>
       <c r="E53">
-        <v>-9.760830098616362</v>
+        <v>-14.12965538937338</v>
       </c>
       <c r="F53">
-        <v>1.454883888209139</v>
+        <v>-0.1600987151865682</v>
       </c>
       <c r="G53">
-        <v>-6.392184368509257</v>
+        <v>-8.747548534464432</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>3.067078846771925</v>
       </c>
       <c r="E54">
-        <v>-8.847023930082287</v>
+        <v>-13.40705891702308</v>
       </c>
       <c r="F54">
-        <v>1.372474585509033</v>
+        <v>0.1445657035216592</v>
       </c>
       <c r="G54">
-        <v>-6.068274508579014</v>
+        <v>-8.719462144153235</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>2.668730532073281</v>
       </c>
       <c r="E55">
-        <v>-8.442177196560651</v>
+        <v>-13.68252481135366</v>
       </c>
       <c r="F55">
-        <v>0.9463706771829958</v>
+        <v>0.1440844220606327</v>
       </c>
       <c r="G55">
-        <v>-6.662573964321679</v>
+        <v>-8.805011022914837</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>2.238759151030008</v>
       </c>
       <c r="E56">
-        <v>-7.587421386642988</v>
+        <v>-12.6988159430114</v>
       </c>
       <c r="F56">
-        <v>0.716589843320441</v>
+        <v>-0.09216513285038355</v>
       </c>
       <c r="G56">
-        <v>-6.520740042920266</v>
+        <v>-9.000004925680496</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>1.774644435004393</v>
       </c>
       <c r="E57">
-        <v>-7.808413761237114</v>
+        <v>-12.68383115655142</v>
       </c>
       <c r="F57">
-        <v>0.9952377270089443</v>
+        <v>0.1210582933650148</v>
       </c>
       <c r="G57">
-        <v>-7.393746926742638</v>
+        <v>-9.263348121841503</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>1.280465226506087</v>
       </c>
       <c r="E58">
-        <v>-6.621097860906456</v>
+        <v>-12.10778905222035</v>
       </c>
       <c r="F58">
-        <v>0.891390275924387</v>
+        <v>0.1388582521163706</v>
       </c>
       <c r="G58">
-        <v>-7.733998742440956</v>
+        <v>-9.824843571796828</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>0.7561564234268158</v>
       </c>
       <c r="E59">
-        <v>-6.052323876393837</v>
+        <v>-11.88528906191531</v>
       </c>
       <c r="F59">
-        <v>0.6743132845511655</v>
+        <v>0.1422189386695282</v>
       </c>
       <c r="G59">
-        <v>-7.509136616180664</v>
+        <v>-9.378359253313816</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>0.2037050546065713</v>
       </c>
       <c r="E60">
-        <v>-7.08899034233899</v>
+        <v>-11.76685193456517</v>
       </c>
       <c r="F60">
-        <v>0.7355462029661048</v>
+        <v>-0.02071595925671779</v>
       </c>
       <c r="G60">
-        <v>-7.69769503352923</v>
+        <v>-9.652514848198917</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-0.3682116358608489</v>
       </c>
       <c r="E61">
-        <v>-7.281873782686676</v>
+        <v>-10.39561937713713</v>
       </c>
       <c r="F61">
-        <v>0.6059497795329278</v>
+        <v>0.01218927908468697</v>
       </c>
       <c r="G61">
-        <v>-8.547538085966949</v>
+        <v>-9.957670424358898</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-0.955820913901728</v>
       </c>
       <c r="E62">
-        <v>-6.317830369967476</v>
+        <v>-10.43618794535806</v>
       </c>
       <c r="F62">
-        <v>1.021260060600488</v>
+        <v>-0.4631826088902541</v>
       </c>
       <c r="G62">
-        <v>-7.623252262258225</v>
+        <v>-10.11127227700475</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-1.547821355656222</v>
       </c>
       <c r="E63">
-        <v>-5.56464549620982</v>
+        <v>-10.38565997638019</v>
       </c>
       <c r="F63">
-        <v>1.337360091304362</v>
+        <v>-0.1142477510742128</v>
       </c>
       <c r="G63">
-        <v>-7.420520112524505</v>
+        <v>-10.20604100028987</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.129476448602149</v>
       </c>
       <c r="E64">
-        <v>-5.461936580146809</v>
+        <v>-11.09657761848507</v>
       </c>
       <c r="F64">
-        <v>0.497026921371418</v>
+        <v>-0.3673081940576421</v>
       </c>
       <c r="G64">
-        <v>-8.567890145426972</v>
+        <v>-10.08920756909296</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.691485246469171</v>
       </c>
       <c r="E65">
-        <v>-4.90867899314375</v>
+        <v>-10.1239079858442</v>
       </c>
       <c r="F65">
-        <v>0.8020922699026003</v>
+        <v>-0.1321272330962373</v>
       </c>
       <c r="G65">
-        <v>-8.074142212238741</v>
+        <v>-10.12511836094372</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.216962417341418</v>
       </c>
       <c r="E66">
-        <v>-5.166215474185043</v>
+        <v>-10.57640866610692</v>
       </c>
       <c r="F66">
-        <v>0.6206483307282022</v>
+        <v>-0.5067746150951753</v>
       </c>
       <c r="G66">
-        <v>-8.444917548324058</v>
+        <v>-10.32694458230433</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.692562228823318</v>
       </c>
       <c r="E67">
-        <v>-5.996836973094127</v>
+        <v>-10.27379738255726</v>
       </c>
       <c r="F67">
-        <v>0.7658329719472604</v>
+        <v>-0.5073652410533713</v>
       </c>
       <c r="G67">
-        <v>-8.294268447810753</v>
+        <v>-10.11632798390544</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.108118189532494</v>
       </c>
       <c r="E68">
-        <v>-5.600603999860185</v>
+        <v>-9.663445599471782</v>
       </c>
       <c r="F68">
-        <v>0.4707593910286457</v>
+        <v>-0.5725602407559008</v>
       </c>
       <c r="G68">
-        <v>-7.67542016067785</v>
+        <v>-10.391320322432</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.452015244198052</v>
       </c>
       <c r="E69">
-        <v>-4.071258687295922</v>
+        <v>-10.65820616314942</v>
       </c>
       <c r="F69">
-        <v>0.1804282134910582</v>
+        <v>-0.520377236216546</v>
       </c>
       <c r="G69">
-        <v>-8.680891003564128</v>
+        <v>-10.08315586313076</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-4.719770547486386</v>
       </c>
       <c r="E70">
-        <v>-5.075322444341171</v>
+        <v>-10.5036568633299</v>
       </c>
       <c r="F70">
-        <v>-0.01977079205012355</v>
+        <v>-0.6594112494698178</v>
       </c>
       <c r="G70">
-        <v>-8.308748942685362</v>
+        <v>-10.82918657301974</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-4.909066365400768</v>
       </c>
       <c r="E71">
-        <v>-5.686185072419602</v>
+        <v>-10.51607081197981</v>
       </c>
       <c r="F71">
-        <v>0.1651746561359081</v>
+        <v>-0.4569549427560075</v>
       </c>
       <c r="G71">
-        <v>-7.778454501338432</v>
+        <v>-9.999297441491905</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.019396630215614</v>
       </c>
       <c r="E72">
-        <v>-6.057536156606496</v>
+        <v>-9.752943150310513</v>
       </c>
       <c r="F72">
-        <v>-0.09236228429224982</v>
+        <v>-0.5387073501056935</v>
       </c>
       <c r="G72">
-        <v>-8.167268777176048</v>
+        <v>-10.375309931227</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.056067960523811</v>
       </c>
       <c r="E73">
-        <v>-6.447219515581184</v>
+        <v>-10.49802510877343</v>
       </c>
       <c r="F73">
-        <v>0.4424872115710985</v>
+        <v>-0.6516560738448088</v>
       </c>
       <c r="G73">
-        <v>-7.76792014691329</v>
+        <v>-10.17278272494368</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.025946970216435</v>
       </c>
       <c r="E74">
-        <v>-5.737161588220547</v>
+        <v>-10.53033293966927</v>
       </c>
       <c r="F74">
-        <v>-0.2312480197804205</v>
+        <v>-0.913426800068675</v>
       </c>
       <c r="G74">
-        <v>-8.49405176152881</v>
+        <v>-10.21377141502416</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-4.93731778241834</v>
       </c>
       <c r="E75">
-        <v>-6.580911388127415</v>
+        <v>-10.51728354968666</v>
       </c>
       <c r="F75">
-        <v>0.1735759583351006</v>
+        <v>-0.9350952345911044</v>
       </c>
       <c r="G75">
-        <v>-7.073419008391403</v>
+        <v>-10.0588171966801</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-4.796807900582007</v>
       </c>
       <c r="E76">
-        <v>-8.547195298120265</v>
+        <v>-11.95050693934909</v>
       </c>
       <c r="F76">
-        <v>0.2483261760289224</v>
+        <v>-0.5894622492426219</v>
       </c>
       <c r="G76">
-        <v>-7.375208029401143</v>
+        <v>-9.505853660048537</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.609613076361567</v>
       </c>
       <c r="E77">
-        <v>-5.059336733951906</v>
+        <v>-11.8726425334312</v>
       </c>
       <c r="F77">
-        <v>0.4086840229650591</v>
+        <v>-1.005997685698923</v>
       </c>
       <c r="G77">
-        <v>-7.452828076839532</v>
+        <v>-9.572938047689489</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.377391106044231</v>
       </c>
       <c r="E78">
-        <v>-9.548123380615268</v>
+        <v>-12.15939685614267</v>
       </c>
       <c r="F78">
-        <v>0.004438245296691999</v>
+        <v>-0.7858896979988576</v>
       </c>
       <c r="G78">
-        <v>-7.283286323092635</v>
+        <v>-9.226471354492027</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.098545160816481</v>
       </c>
       <c r="E79">
-        <v>-7.454651527010869</v>
+        <v>-12.64609507845402</v>
       </c>
       <c r="F79">
-        <v>-0.4243702825994861</v>
+        <v>-0.7088838358672127</v>
       </c>
       <c r="G79">
-        <v>-6.804099817861339</v>
+        <v>-9.510807547910176</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.77257278285198</v>
       </c>
       <c r="E80">
-        <v>-9.99437347783412</v>
+        <v>-13.34211515153674</v>
       </c>
       <c r="F80">
-        <v>0.4172551404818256</v>
+        <v>-0.6919520061539908</v>
       </c>
       <c r="G80">
-        <v>-6.387237007509098</v>
+        <v>-9.174518842501168</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.394097218285542</v>
       </c>
       <c r="E81">
-        <v>-10.54872335941561</v>
+        <v>-14.16548099026135</v>
       </c>
       <c r="F81">
-        <v>-0.2544091723626947</v>
+        <v>-0.9496629037367366</v>
       </c>
       <c r="G81">
-        <v>-5.961555101928076</v>
+        <v>-9.028073040779555</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-2.960466025350476</v>
       </c>
       <c r="E82">
-        <v>-10.32483204331675</v>
+        <v>-15.03043708719279</v>
       </c>
       <c r="F82">
-        <v>0.2345131495872407</v>
+        <v>-0.8546417073290081</v>
       </c>
       <c r="G82">
-        <v>-5.832892386988831</v>
+        <v>-9.017747545921702</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.473205997831864</v>
       </c>
       <c r="E83">
-        <v>-11.76570980145084</v>
+        <v>-15.8647590973923</v>
       </c>
       <c r="F83">
-        <v>0.287991720744574</v>
+        <v>-0.8734091992068337</v>
       </c>
       <c r="G83">
-        <v>-6.245925235025909</v>
+        <v>-8.486769089491901</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-1.929516007718574</v>
       </c>
       <c r="E84">
-        <v>-11.57281390146918</v>
+        <v>-17.09889830219907</v>
       </c>
       <c r="F84">
-        <v>-0.1068827364959224</v>
+        <v>-0.7852584820379243</v>
       </c>
       <c r="G84">
-        <v>-5.76544380047742</v>
+        <v>-8.230169446609739</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-1.337462232256091</v>
       </c>
       <c r="E85">
-        <v>-14.06110248324576</v>
+        <v>-17.40869464134068</v>
       </c>
       <c r="F85">
-        <v>-0.03705799137914643</v>
+        <v>-0.6809869068431337</v>
       </c>
       <c r="G85">
-        <v>-5.697394742710052</v>
+        <v>-8.26886590293922</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-0.7068074230743225</v>
       </c>
       <c r="E86">
-        <v>-14.18382157147179</v>
+        <v>-18.61057170057619</v>
       </c>
       <c r="F86">
-        <v>-0.1235072419027056</v>
+        <v>-0.5765165234716713</v>
       </c>
       <c r="G86">
-        <v>-5.394339510573622</v>
+        <v>-7.880115590344088</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-0.04715288635590456</v>
       </c>
       <c r="E87">
-        <v>-16.67462284609989</v>
+        <v>-19.67294239141071</v>
       </c>
       <c r="F87">
-        <v>-0.05261473120372115</v>
+        <v>-0.6410115527188351</v>
       </c>
       <c r="G87">
-        <v>-5.07981266670384</v>
+        <v>-8.049605129199163</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>0.6214241886796275</v>
       </c>
       <c r="E88">
-        <v>-17.2889617120572</v>
+        <v>-19.93557901595889</v>
       </c>
       <c r="F88">
-        <v>-0.1099568079277113</v>
+        <v>-0.6302195821951633</v>
       </c>
       <c r="G88">
-        <v>-4.952353505021098</v>
+        <v>-7.787632573948491</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.28174615583884</v>
       </c>
       <c r="E89">
-        <v>-18.49316872284594</v>
+        <v>-22.28028692902482</v>
       </c>
       <c r="F89">
-        <v>-0.1645213687501147</v>
+        <v>-0.6548303777323365</v>
       </c>
       <c r="G89">
-        <v>-5.503343318741784</v>
+        <v>-7.67143094294263</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.915843478756398</v>
       </c>
       <c r="E90">
-        <v>-20.30436756875837</v>
+        <v>-23.4102469809596</v>
       </c>
       <c r="F90">
-        <v>0.001767588790066393</v>
+        <v>-0.4662923001203634</v>
       </c>
       <c r="G90">
-        <v>-4.648995426512099</v>
+        <v>-7.503017030859094</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.5032790842656</v>
       </c>
       <c r="E91">
-        <v>-23.31180756613851</v>
+        <v>-25.63198661312</v>
       </c>
       <c r="F91">
-        <v>-0.2107923151356896</v>
+        <v>-0.7440985625276224</v>
       </c>
       <c r="G91">
-        <v>-4.65389840485421</v>
+        <v>-7.161239234947272</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>3.031637185071579</v>
       </c>
       <c r="E92">
-        <v>-24.31825526648421</v>
+        <v>-27.11597885801713</v>
       </c>
       <c r="F92">
-        <v>0.1732570368850228</v>
+        <v>-0.5399465877402815</v>
       </c>
       <c r="G92">
-        <v>-4.260991786870025</v>
+        <v>-7.277824645408026</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>3.486284527053191</v>
       </c>
       <c r="E93">
-        <v>-25.39171087834469</v>
+        <v>-28.08626662396322</v>
       </c>
       <c r="F93">
-        <v>0.1888783893670159</v>
+        <v>-0.4304007972918665</v>
       </c>
       <c r="G93">
-        <v>-4.588329554448399</v>
+        <v>-7.373735569451755</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>3.852395511812015</v>
       </c>
       <c r="E94">
-        <v>-28.48638907960286</v>
+        <v>-30.98489040802719</v>
       </c>
       <c r="F94">
-        <v>-0.2129651228332327</v>
+        <v>-0.6514257877068306</v>
       </c>
       <c r="G94">
-        <v>-4.421064369984953</v>
+        <v>-7.063239715230652</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>4.122270128455182</v>
       </c>
       <c r="E95">
-        <v>-29.81616012837514</v>
+        <v>-33.04605443073574</v>
       </c>
       <c r="F95">
-        <v>-0.405315347232889</v>
+        <v>-0.7623740041681851</v>
       </c>
       <c r="G95">
-        <v>-4.887565267248031</v>
+        <v>-7.360689678729962</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>4.280843131553606</v>
       </c>
       <c r="E96">
-        <v>-32.73850497892087</v>
+        <v>-34.33941427582325</v>
       </c>
       <c r="F96">
-        <v>-0.718806848985348</v>
+        <v>-0.8266669117690659</v>
       </c>
       <c r="G96">
-        <v>-4.988052826559981</v>
+        <v>-7.40589733206968</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>4.327593444976217</v>
       </c>
       <c r="E97">
-        <v>-33.62976751638377</v>
+        <v>-36.65204278461621</v>
       </c>
       <c r="F97">
-        <v>-0.537671890852194</v>
+        <v>-0.8019591972457651</v>
       </c>
       <c r="G97">
-        <v>-5.22321303485992</v>
+        <v>-7.239253504818919</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>4.252554007163594</v>
       </c>
       <c r="E98">
-        <v>-37.16906775602146</v>
+        <v>-38.73507969476697</v>
       </c>
       <c r="F98">
-        <v>-1.000902397804303</v>
+        <v>-0.8922504157835084</v>
       </c>
       <c r="G98">
-        <v>-5.605637513310785</v>
+        <v>-7.701937493489789</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>4.077784992468668</v>
       </c>
       <c r="E99">
-        <v>-39.54446790077787</v>
+        <v>-40.90538388127504</v>
       </c>
       <c r="F99">
-        <v>-0.26030797663803</v>
+        <v>-0.6115970546128275</v>
       </c>
       <c r="G99">
-        <v>-5.015977350706529</v>
+        <v>-7.815203342202943</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.794668863606812</v>
       </c>
       <c r="E100">
-        <v>-42.32118662603548</v>
+        <v>-44.1542479763618</v>
       </c>
       <c r="F100">
-        <v>-0.8545447883428805</v>
+        <v>-0.7838452872487484</v>
       </c>
       <c r="G100">
-        <v>-5.311148134177797</v>
+        <v>-7.772723916960938</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.469424665587723</v>
       </c>
       <c r="E101">
-        <v>-44.28777372045504</v>
+        <v>-45.76790763203141</v>
       </c>
       <c r="F101">
-        <v>-0.874151416399742</v>
+        <v>-1.189608633999044</v>
       </c>
       <c r="G101">
-        <v>-5.423522413613086</v>
+        <v>-7.74905360112561</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.065664912410321</v>
       </c>
       <c r="E102">
-        <v>-46.4838963451639</v>
+        <v>-47.35917628714603</v>
       </c>
       <c r="F102">
-        <v>-1.202483120173354</v>
+        <v>-1.25058890035613</v>
       </c>
       <c r="G102">
-        <v>-6.45888367132302</v>
+        <v>-7.824083789929615</v>
       </c>
     </row>
   </sheetData>
